--- a/services/integrator/internal/document/testdata/stok-nilai-kolom-akhir.golden.xlsx
+++ b/services/integrator/internal/document/testdata/stok-nilai-kolom-akhir.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">Kopi Arabika</t>
@@ -267,21 +270,21 @@
         <v>10</v>
       </c>
       <c r="B10" s="7">
-        <v>9.666</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="8">
-        <v>840461.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7">
-        <v>0</v>
+        <v>9.666</v>
       </c>
       <c r="C11" s="8">
-        <v>0</v>
+        <v>840461.99</v>
       </c>
     </row>
     <row r="12">
@@ -289,10 +292,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C12" s="8">
-        <v>304500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -300,7 +303,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7">
-        <v>1</v>
+        <v>2.9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>304500</v>
       </c>
     </row>
     <row r="14">
@@ -308,7 +314,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>5.551115123125783e-17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -316,10 +322,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-87500</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="16">
@@ -327,10 +330,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
       <c r="C16" s="8">
-        <v>200</v>
+        <v>-87500</v>
       </c>
     </row>
     <row r="17">
@@ -338,10 +341,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
       <c r="C17" s="8">
-        <v>211296.7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
@@ -349,10 +352,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="C18" s="8">
-        <v>3</v>
+        <v>211296.7</v>
       </c>
     </row>
     <row r="19">
@@ -360,20 +363,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="7">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="10">
-        <v>10033886.68</v>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" s="9" t="s">
         <v>20</v>
+      </c>
+      <c r="C21" s="10">
+        <v>10033887.71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
